--- a/AAII_Financials/Yearly/AIAGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AIAGY_YR_FIN.xlsx
@@ -711,25 +711,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21384500</v>
+        <v>21320000</v>
       </c>
       <c r="E8" s="3">
-        <v>19164600</v>
+        <v>19114400</v>
       </c>
       <c r="F8" s="3">
-        <v>18108200</v>
+        <v>18060700</v>
       </c>
       <c r="G8" s="3">
-        <v>18187500</v>
+        <v>18160900</v>
       </c>
       <c r="H8" s="3">
-        <v>18928800</v>
+        <v>18891800</v>
       </c>
       <c r="I8" s="3">
-        <v>14620800</v>
+        <v>14594300</v>
       </c>
       <c r="J8" s="3">
-        <v>12994300</v>
+        <v>12972500</v>
       </c>
       <c r="K8" s="3">
         <v>12132800</v>
@@ -771,25 +771,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2165900</v>
+        <v>2101400</v>
       </c>
       <c r="E10" s="3">
-        <v>1867100</v>
+        <v>1816900</v>
       </c>
       <c r="F10" s="3">
-        <v>1150000</v>
+        <v>1102500</v>
       </c>
       <c r="G10" s="3">
-        <v>1770500</v>
+        <v>1743900</v>
       </c>
       <c r="H10" s="3">
-        <v>2133800</v>
+        <v>2096800</v>
       </c>
       <c r="I10" s="3">
-        <v>1609800</v>
+        <v>1583400</v>
       </c>
       <c r="J10" s="3">
-        <v>1266700</v>
+        <v>1244900</v>
       </c>
       <c r="K10" s="3">
         <v>1136800</v>
@@ -946,25 +946,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>20582000</v>
+        <v>20517400</v>
       </c>
       <c r="E17" s="3">
-        <v>18631500</v>
+        <v>18581300</v>
       </c>
       <c r="F17" s="3">
-        <v>18039100</v>
+        <v>17991500</v>
       </c>
       <c r="G17" s="3">
-        <v>17348000</v>
+        <v>17321500</v>
       </c>
       <c r="H17" s="3">
-        <v>17954400</v>
+        <v>17917500</v>
       </c>
       <c r="I17" s="3">
-        <v>14132800</v>
+        <v>14106300</v>
       </c>
       <c r="J17" s="3">
-        <v>12723000</v>
+        <v>12701200</v>
       </c>
       <c r="K17" s="3">
         <v>11745200</v>
